--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK BULL L.E MATURE BULL PRIVATE LANDS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK BULL L.E MATURE BULL PRIVATE LANDS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$132</definedName>
@@ -642,7 +642,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -691,7 +695,11 @@
       <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="28" customHeight="1">
@@ -736,7 +744,11 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="28" customHeight="1">
@@ -781,7 +793,11 @@
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="28" customHeight="1">
@@ -826,7 +842,11 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -871,7 +891,11 @@
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -916,7 +940,11 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -961,7 +989,11 @@
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
@@ -1006,7 +1038,11 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
@@ -1051,7 +1087,11 @@
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
@@ -1096,7 +1136,11 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
@@ -1141,7 +1185,11 @@
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
@@ -1186,7 +1234,11 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
@@ -1231,7 +1283,11 @@
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
@@ -1284,7 +1340,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -1341,7 +1401,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -1390,7 +1454,11 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr"/>
     </row>
     <row r="19" ht="28" customHeight="1">
@@ -1435,7 +1503,11 @@
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="28" customHeight="1">
@@ -1480,7 +1552,11 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="3" t="inlineStr"/>
       <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="28" customHeight="1">
@@ -1525,7 +1601,11 @@
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
@@ -1578,7 +1658,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -1627,7 +1711,11 @@
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="28" customHeight="1">
@@ -1672,7 +1760,11 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="28" customHeight="1">
@@ -1725,7 +1817,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -1782,7 +1878,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -1831,7 +1931,11 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="28" customHeight="1">
@@ -1876,7 +1980,11 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr"/>
       <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="28" customHeight="1">
@@ -1921,7 +2029,11 @@
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="28" customHeight="1">
@@ -1966,7 +2078,11 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr"/>
       <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1">
@@ -2011,7 +2127,11 @@
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -2056,7 +2176,11 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr"/>
     </row>
     <row r="33" ht="28" customHeight="1">
@@ -2109,7 +2233,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -2158,7 +2286,11 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr"/>
       <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="28" customHeight="1">
@@ -2203,7 +2335,11 @@
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="28" customHeight="1">
@@ -2248,7 +2384,11 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr"/>
     </row>
     <row r="37" ht="28" customHeight="1">
@@ -2293,7 +2433,11 @@
       <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O37" s="5" t="inlineStr"/>
     </row>
     <row r="38" ht="28" customHeight="1">
@@ -2346,7 +2490,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -2395,7 +2543,11 @@
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="28" customHeight="1">
@@ -2440,7 +2592,11 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr"/>
     </row>
     <row r="41" ht="28" customHeight="1">
@@ -2493,7 +2649,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -2550,7 +2710,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -2599,7 +2763,11 @@
       <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O43" s="5" t="inlineStr"/>
     </row>
     <row r="44" ht="28" customHeight="1">
@@ -2652,7 +2820,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -2701,7 +2873,11 @@
       <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="28" customHeight="1">
@@ -2754,7 +2930,11 @@
           <t>57.1</t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -2803,7 +2983,11 @@
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O47" s="5" t="inlineStr"/>
     </row>
     <row r="48" ht="28" customHeight="1">
@@ -2848,7 +3032,11 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="3" t="inlineStr"/>
       <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O48" s="3" t="inlineStr"/>
     </row>
     <row r="49" ht="28" customHeight="1">
@@ -2893,7 +3081,11 @@
       <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="28" customHeight="1">
@@ -2938,7 +3130,11 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="inlineStr"/>
       <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O50" s="3" t="inlineStr"/>
     </row>
     <row r="51" ht="28" customHeight="1">
@@ -2983,7 +3179,11 @@
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="28" customHeight="1">
@@ -3036,7 +3236,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="N52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -3085,7 +3289,11 @@
       <c r="K53" s="4" t="inlineStr"/>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="28" customHeight="1">
@@ -3130,7 +3338,11 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="3" t="inlineStr"/>
       <c r="M54" s="3" t="inlineStr"/>
-      <c r="N54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O54" s="3" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1">
@@ -3175,7 +3387,11 @@
       <c r="K55" s="4" t="inlineStr"/>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O55" s="5" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1">
@@ -3220,7 +3436,11 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
-      <c r="N56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O56" s="3" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
@@ -3265,7 +3485,11 @@
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
@@ -3310,7 +3534,11 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr"/>
       <c r="M58" s="3" t="inlineStr"/>
-      <c r="N58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O58" s="3" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1">
@@ -3355,7 +3583,11 @@
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
@@ -3400,7 +3632,11 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr"/>
       <c r="M60" s="3" t="inlineStr"/>
-      <c r="N60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O60" s="3" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
@@ -3445,7 +3681,11 @@
       <c r="K61" s="4" t="inlineStr"/>
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
-      <c r="N61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
@@ -3498,7 +3738,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
           <t>7.0</t>
@@ -3555,7 +3799,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -3612,7 +3860,11 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="N64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -3661,7 +3913,11 @@
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
-      <c r="N65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O65" s="5" t="inlineStr"/>
     </row>
     <row r="66" ht="28" customHeight="1">
@@ -3841,7 +4097,11 @@
       <c r="K69" s="4" t="inlineStr"/>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr"/>
-      <c r="N69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
       <c r="O69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="28" customHeight="1">
@@ -4029,7 +4289,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
           <t>6.0</t>
@@ -4078,7 +4342,11 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr"/>
       <c r="M74" s="3" t="inlineStr"/>
-      <c r="N74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O74" s="3" t="inlineStr"/>
     </row>
     <row r="75" ht="28" customHeight="1">
@@ -4123,7 +4391,11 @@
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="5" t="inlineStr"/>
       <c r="M75" s="5" t="inlineStr"/>
-      <c r="N75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O75" s="5" t="inlineStr"/>
     </row>
     <row r="76" ht="28" customHeight="1">
@@ -4168,7 +4440,11 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="3" t="inlineStr"/>
       <c r="M76" s="3" t="inlineStr"/>
-      <c r="N76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O76" s="3" t="inlineStr"/>
     </row>
     <row r="77" ht="28" customHeight="1">
@@ -4266,7 +4542,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -4315,7 +4595,11 @@
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="5" t="inlineStr"/>
       <c r="M79" s="5" t="inlineStr"/>
-      <c r="N79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="28" customHeight="1">
@@ -4409,7 +4693,11 @@
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr"/>
-      <c r="N81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O81" s="5" t="inlineStr"/>
     </row>
     <row r="82" ht="28" customHeight="1">
@@ -4454,7 +4742,11 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
-      <c r="N82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O82" s="3" t="inlineStr"/>
     </row>
     <row r="83" ht="28" customHeight="1">
@@ -4499,7 +4791,11 @@
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="5" t="inlineStr"/>
       <c r="M83" s="5" t="inlineStr"/>
-      <c r="N83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O83" s="5" t="inlineStr"/>
     </row>
     <row r="84" ht="28" customHeight="1">
@@ -4544,7 +4840,11 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr"/>
       <c r="M84" s="3" t="inlineStr"/>
-      <c r="N84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O84" s="3" t="inlineStr"/>
     </row>
     <row r="85" ht="28" customHeight="1">
@@ -4589,7 +4889,11 @@
       <c r="K85" s="4" t="inlineStr"/>
       <c r="L85" s="5" t="inlineStr"/>
       <c r="M85" s="5" t="inlineStr"/>
-      <c r="N85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="28" customHeight="1">
@@ -4634,7 +4938,11 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="inlineStr"/>
       <c r="M86" s="3" t="inlineStr"/>
-      <c r="N86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O86" s="3" t="inlineStr"/>
     </row>
     <row r="87" ht="28" customHeight="1">
@@ -5525,7 +5833,11 @@
       <c r="K105" s="4" t="inlineStr"/>
       <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="5" t="inlineStr"/>
-      <c r="N105" s="5" t="inlineStr"/>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="28" customHeight="1">
@@ -5578,7 +5890,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N106" s="3" t="inlineStr"/>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O106" s="3" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -5627,7 +5943,11 @@
       <c r="K107" s="4" t="inlineStr"/>
       <c r="L107" s="5" t="inlineStr"/>
       <c r="M107" s="5" t="inlineStr"/>
-      <c r="N107" s="5" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O107" s="5" t="inlineStr"/>
     </row>
     <row r="108" ht="28" customHeight="1">
@@ -5680,7 +6000,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N108" s="3" t="inlineStr"/>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -5729,7 +6053,11 @@
       <c r="K109" s="4" t="inlineStr"/>
       <c r="L109" s="5" t="inlineStr"/>
       <c r="M109" s="5" t="inlineStr"/>
-      <c r="N109" s="5" t="inlineStr"/>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="28" customHeight="1">
@@ -5774,7 +6102,11 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
-      <c r="N110" s="3" t="inlineStr"/>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O110" s="3" t="inlineStr"/>
     </row>
     <row r="111" ht="28" customHeight="1">
@@ -5819,7 +6151,11 @@
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr"/>
       <c r="M111" s="5" t="inlineStr"/>
-      <c r="N111" s="5" t="inlineStr"/>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O111" s="5" t="inlineStr"/>
     </row>
     <row r="112" ht="28" customHeight="1">
@@ -5864,7 +6200,11 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="3" t="inlineStr"/>
       <c r="M112" s="3" t="inlineStr"/>
-      <c r="N112" s="3" t="inlineStr"/>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O112" s="3" t="inlineStr"/>
     </row>
     <row r="113" ht="28" customHeight="1">
@@ -5909,7 +6249,11 @@
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="inlineStr"/>
-      <c r="N113" s="5" t="inlineStr"/>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O113" s="5" t="inlineStr"/>
     </row>
     <row r="114" ht="28" customHeight="1">
@@ -5954,7 +6298,11 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="3" t="inlineStr"/>
       <c r="M114" s="3" t="inlineStr"/>
-      <c r="N114" s="3" t="inlineStr"/>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O114" s="3" t="inlineStr"/>
     </row>
     <row r="115" ht="28" customHeight="1">
@@ -6134,7 +6482,11 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="3" t="inlineStr"/>
       <c r="M118" s="3" t="inlineStr"/>
-      <c r="N118" s="3" t="inlineStr"/>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O118" s="3" t="inlineStr"/>
     </row>
     <row r="119" ht="28" customHeight="1">
@@ -6187,7 +6539,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N119" s="5" t="inlineStr"/>
+      <c r="N119" s="5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O119" s="5" t="inlineStr">
         <is>
           <t>11.0</t>
@@ -6236,7 +6592,11 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr"/>
       <c r="M120" s="3" t="inlineStr"/>
-      <c r="N120" s="3" t="inlineStr"/>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O120" s="3" t="inlineStr"/>
     </row>
     <row r="121" ht="28" customHeight="1">
@@ -6289,7 +6649,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O121" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -6440,7 +6804,11 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="3" t="inlineStr"/>
       <c r="M124" s="3" t="inlineStr"/>
-      <c r="N124" s="3" t="inlineStr"/>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O124" s="3" t="inlineStr"/>
     </row>
     <row r="125" ht="28" customHeight="1">
